--- a/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
@@ -54,6 +54,9 @@
     <t xml:space="preserve">Los Vilos</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
@@ -75,16 +78,13 @@
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -520,7 +520,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>156.93</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="3">
@@ -537,7 +537,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>144.6</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="4">
@@ -554,7 +554,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>140.1</v>
+        <v>150.69</v>
       </c>
     </row>
     <row r="5">
@@ -571,7 +571,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>107.63</v>
+        <v>115.57</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>99.05</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="7">
@@ -605,7 +605,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>98.85</v>
+        <v>105.43</v>
       </c>
     </row>
     <row r="8">
@@ -616,13 +616,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>94</v>
+        <v>105.14</v>
       </c>
     </row>
     <row r="9">
@@ -633,13 +633,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4204</v>
+        <v>4106</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>93.11</v>
+        <v>100.77</v>
       </c>
     </row>
     <row r="10">
@@ -650,13 +650,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4303</v>
+        <v>4204</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.02</v>
+        <v>100.67</v>
       </c>
     </row>
     <row r="11">
@@ -667,13 +667,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4103</v>
+        <v>4303</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>90.43</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="12">
@@ -684,13 +684,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4301</v>
+        <v>4103</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>88.99</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="13">
@@ -701,13 +701,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>83.22</v>
+        <v>95.59</v>
       </c>
     </row>
     <row r="14">
@@ -715,16 +715,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>79.79</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="15">
@@ -732,16 +732,16 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.17</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="16">
@@ -752,10 +752,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4104</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>72.96</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:07</t>
+    <t xml:space="preserve">2026-10-04 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:39</t>
+    <t xml:space="preserve">2026-10-05 16:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
